--- a/Config/Datas/rumor_tables.xlsx
+++ b/Config/Datas/rumor_tables.xlsx
@@ -106,10 +106,10 @@
     <t>北巷库房有人藏了一批物资，夜半可取之。</t>
   </si>
   <si>
-    <t>evil_scroll_01</t>
-  </si>
-  <si>
-    <t>spoil_small</t>
+    <t>rumor_points</t>
+  </si>
+  <si>
+    <t>rumor_gold_chest</t>
   </si>
   <si>
     <t/>
@@ -185,14 +185,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,148 +641,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1147,6 +1140,8 @@
     <col min="2" max="2" width="19.5" customWidth="1"/>
     <col min="3" max="3" width="14.25" customWidth="1"/>
     <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="23.625" customWidth="1"/>
+    <col min="8" max="8" width="12.75" customWidth="1"/>
     <col min="9" max="9" width="23.375" customWidth="1"/>
     <col min="12" max="12" width="14.375" customWidth="1"/>
   </cols>
@@ -1317,7 +1312,7 @@
         <v>25</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -1352,7 +1347,7 @@
         <v>25</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1387,7 +1382,7 @@
         <v>25</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1422,7 +1417,7 @@
         <v>25</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="G8">
         <v>1</v>

--- a/Config/Datas/rumor_tables.xlsx
+++ b/Config/Datas/rumor_tables.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="rumor_intel" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/rumor_tables.xlsx
+++ b/Config/Datas/rumor_tables.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rumor_intel" sheetId="1" r:id="Rb121768d748c4c2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rumor_random_pool" sheetId="2" r:id="Re32ac5c8f8b04e33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rumor_global" sheetId="3" r:id="Rb5461f9542384acf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rumor_intel" sheetId="1" r:id="R9cffef0653004af4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rumor_random_pool" sheetId="2" r:id="R72e80f95977a4cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rumor_global" sheetId="3" r:id="R597720f0f05b4161"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -942,13 +942,18 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <x:cols>
-    <x:col min="2" max="2" width="19.5" customWidth="1"/>
-    <x:col min="3" max="3" width="14.25" customWidth="1"/>
-    <x:col min="4" max="4" width="18.5" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="23.625" customWidth="1"/>
     <x:col min="8" max="8" width="12.75" customWidth="1"/>
     <x:col min="9" max="9" width="23.375" customWidth="1"/>
     <x:col min="12" max="12" width="14.375" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -991,6 +996,18 @@
       <x:c r="M1" t="str">
         <x:v>interact_point_cfg_id</x:v>
       </x:c>
+      <x:c r="N1" t="str">
+        <x:v>target_overlay_id</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>event_group_cfg_id</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>cult_action_id</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>event_expire_days</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
@@ -1032,6 +1049,18 @@
       <x:c r="M2" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="N2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
@@ -1070,6 +1099,18 @@
       <x:c r="M3" t="str">
         <x:v>c,s</x:v>
       </x:c>
+      <x:c r="N3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
+      <x:c r="Q3" t="str">
+        <x:v>c,s</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
@@ -1111,6 +1152,18 @@
       <x:c r="M4" t="str">
         <x:v>interact_point_cfg_id</x:v>
       </x:c>
+      <x:c r="N4" t="str">
+        <x:v>target_overlay_id</x:v>
+      </x:c>
+      <x:c r="O4" t="str">
+        <x:v>event_group_cfg_id</x:v>
+      </x:c>
+      <x:c r="P4" t="str">
+        <x:v>cult_action_id</x:v>
+      </x:c>
+      <x:c r="Q4" t="str">
+        <x:v>event_expire_days</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" t="s">
@@ -1146,6 +1199,12 @@
       <x:c r="L5" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="N5" t="str"/>
+      <x:c r="O5" t="str"/>
+      <x:c r="P5" t="str"/>
+      <x:c r="Q5" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" t="s">
@@ -1181,6 +1240,12 @@
       <x:c r="L6" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="N6" t="str"/>
+      <x:c r="O6" t="str"/>
+      <x:c r="P6" t="str"/>
+      <x:c r="Q6" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="B7" t="s">
@@ -1216,6 +1281,12 @@
       <x:c r="L7" t="s">
         <x:v>28</x:v>
       </x:c>
+      <x:c r="N7" t="str"/>
+      <x:c r="O7" t="str"/>
+      <x:c r="P7" t="str"/>
+      <x:c r="Q7" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="B8" t="s">
@@ -1250,6 +1321,12 @@
       </x:c>
       <x:c r="L8" t="s">
         <x:v>28</x:v>
+      </x:c>
+      <x:c r="N8" t="str"/>
+      <x:c r="O8" t="str"/>
+      <x:c r="P8" t="str"/>
+      <x:c r="Q8" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1258,10 +1335,10 @@
         <x:v>rumor_cult_influence_demo</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Cult influence lead</x:v>
+        <x:v>教团仪式的隐秘线索</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>A discreet contact point has been prepared. Use it to establish influence in this area.</x:v>
+        <x:v>有人在这片地区筹备隐秘仪式。进入冒险并解决该事件，可推进当地教团锚点。</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>rumor_points</x:v>
@@ -1283,8 +1360,18 @@
       <x:c r="L9" t="str">
         <x:v>0,0,0,0,0,"",""</x:v>
       </x:c>
-      <x:c r="M9" t="str">
-        <x:v>cult_influence_point</x:v>
+      <x:c r="M9" t="str"/>
+      <x:c r="N9" t="str">
+        <x:v>village_01</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>rumor_cult_smear_demo</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>rumor_cult_influence_demo</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
